--- a/data/trans_camb/IP13-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,86</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4,11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,49</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,21</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 7,62</t>
+          <t>-5,79; 4,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 9,31</t>
+          <t>-8,01; 0,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 9,66</t>
+          <t>-6,53; 3,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 3,55</t>
+          <t>-0,72; 7,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 0,63</t>
+          <t>-0,11; 9,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 2,74</t>
+          <t>0,97; 10,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 4,34</t>
+          <t>-2,38; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,82</t>
+          <t>-2,75; 4,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 4,71</t>
+          <t>-1,57; 5,06</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-26,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-59,62%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-24,53%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>153,48%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>220,26%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>240,95%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-26,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-59,62%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-31,39%</t>
+          <t>255,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 1159,96</t>
+          <t>-82,75; 232,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; 1574,54</t>
+          <t>-100,0; 78,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 1485,5</t>
+          <t>-80,99; 140,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-82,46; 149,98</t>
+          <t>-50,3; 1160,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,46</t>
+          <t>-41,65; 1490,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,71; 134,22</t>
+          <t>-3,27; 1527,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 200,23</t>
+          <t>-51,27; 177,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-54,2; 183,19</t>
+          <t>-55,88; 198,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 219,68</t>
+          <t>-31,92; 237,83</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,35</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,82</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-2,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,03</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>2,43</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 10,1</t>
+          <t>-7,37; 2,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 1,0</t>
+          <t>-5,43; 4,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 6,05</t>
+          <t>-1,11; 11,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,28</t>
+          <t>-1,42; 10,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 4,17</t>
+          <t>-7,01; 0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 10,37</t>
+          <t>-4,49; 5,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 4,44</t>
+          <t>-3,01; 4,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 1,68</t>
+          <t>-4,96; 1,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 6,56</t>
+          <t>-1,69; 6,75</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-42,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-12,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>82,57%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>86,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-60,4%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-42,39%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-12,59%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,01; 562,94</t>
+          <t>-89,45; 153,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 122,06</t>
+          <t>-70,16; 179,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 309,27</t>
+          <t>-26,24; 506,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,59; 117,14</t>
+          <t>-30,34; 459,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,36; 192,81</t>
+          <t>-100,0; 94,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,11; 423,95</t>
+          <t>-67,54; 333,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,49; 142,94</t>
+          <t>-45,59; 153,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-72,17; 70,66</t>
+          <t>-70,9; 60,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 209,82</t>
+          <t>-28,72; 200,22</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,27</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,15</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,27</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>1,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 6,92</t>
+          <t>-3,08; 6,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 7,23</t>
+          <t>-1,54; 9,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,24</t>
+          <t>-2,25; 10,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 5,83</t>
+          <t>-6,14; 6,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 9,93</t>
+          <t>-5,97; 7,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 7,7</t>
+          <t>-7,08; 5,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,51</t>
+          <t>-2,46; 5,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 6,6</t>
+          <t>-2,0; 6,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 5,31</t>
+          <t>-2,91; 5,56</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33,92%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78,02%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>9,45%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-10,63%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>33,92%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,92%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>-18,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,72; 264,59</t>
+          <t>-69,13; 528,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 286,68</t>
+          <t>-45,01; 565,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-77,64; 295,21</t>
+          <t>-57,09; 787,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 369,62</t>
+          <t>-66,91; 201,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 708,15</t>
+          <t>-68,8; 289,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 465,3</t>
+          <t>-81,1; 215,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 185,06</t>
+          <t>-44,25; 188,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 234,22</t>
+          <t>-38,64; 225,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 199,4</t>
+          <t>-50,42; 225,8</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,93</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,9</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,78</t>
+          <t>-0,77; 7,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 6,48</t>
+          <t>-4,44; 2,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 2,38</t>
+          <t>-2,48; 5,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 6,94</t>
+          <t>-4,33; 2,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 2,58</t>
+          <t>-1,41; 5,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,16</t>
+          <t>-3,97; 3,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,19</t>
+          <t>-1,58; 4,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,47</t>
+          <t>-1,73; 3,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,82</t>
+          <t>-1,84; 3,64</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>56,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-16,44%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-17,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>45,81%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-23,4%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>56,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-16,44%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>-6,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 78,91</t>
+          <t>-14,03; 224,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 175,07</t>
+          <t>-63,45; 71,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,83; 70,57</t>
+          <t>-36,24; 148,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 193,07</t>
+          <t>-63,12; 68,19</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,12; 68,71</t>
+          <t>-22,71; 155,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 162,78</t>
+          <t>-57,67; 91,86</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,17; 104,39</t>
+          <t>-25,22; 100,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 84,35</t>
+          <t>-26,84; 86,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 68,82</t>
+          <t>-29,13; 88,22</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,16</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,53</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,55</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,16</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,16</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,01</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,37</t>
+          <t>-4,0; 4,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 3,59</t>
+          <t>-4,73; 3,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 10,64</t>
+          <t>-2,99; 6,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 4,82</t>
+          <t>-1,11; 7,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,92</t>
+          <t>-3,84; 3,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 5,6</t>
+          <t>-0,07; 9,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 5,08</t>
+          <t>-1,51; 5,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,81</t>
+          <t>-3,36; 2,4</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 6,78</t>
+          <t>-0,18; 6,62</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,15%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>104,52%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>4,55%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>150,01%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3,33%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-11,15%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>137,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,34%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,86; 600,83</t>
+          <t>-59,92; 186,08</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 244,63</t>
+          <t>-70,12; 135,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 844,03</t>
+          <t>-45,64; 223,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,16; 195,41</t>
+          <t>-26,6; 614,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-67,23; 169,25</t>
+          <t>-70,81; 337,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 208,58</t>
+          <t>-14,34; 783,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 188,02</t>
+          <t>-26,72; 199,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 104,99</t>
+          <t>-56,12; 88,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 260,99</t>
+          <t>-6,12; 236,56</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,01</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,04</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-2,77</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-0,49</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,13</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,01</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,62</t>
+          <t>-0,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 2,09</t>
+          <t>-6,46; 8,29</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 6,12</t>
+          <t>-9,88; 1,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 7,51</t>
+          <t>-8,81; 5,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 7,71</t>
+          <t>-7,8; 2,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,53; 2,19</t>
+          <t>-6,04; 6,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 3,89</t>
+          <t>-4,27; 7,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 3,89</t>
+          <t>-4,84; 4,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 1,9</t>
+          <t>-6,3; 1,67</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 4,07</t>
+          <t>-4,62; 3,69</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-56,02%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-28,54%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-64,38%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-11,27%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>26,13%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7,01%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-56,02%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-33,53%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-10,86%</t>
+          <t>-7,9%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 446,34</t>
+          <t>-66,67; 245,82</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 463,02</t>
+          <t>-91,48; 118,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-71,81; 415,59</t>
+          <t>-86,05; 178,26</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 182,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-93,0; 124,64</t>
+          <t>-100,0; 520,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-87,65; 131,62</t>
+          <t>-70,59; 619,34</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 115,7</t>
+          <t>-63,94; 125,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-79,57; 78,25</t>
+          <t>-80,78; 57,97</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 115,42</t>
+          <t>-61,77; 125,43</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,77</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,33</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,77</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,92</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,05</t>
+          <t>1,64</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,24</t>
+          <t>-1,24; 2,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 2,67</t>
+          <t>-2,62; 1,13</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,41</t>
+          <t>-1,04; 3,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,67</t>
+          <t>-0,45; 3,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,75</t>
+          <t>-0,84; 2,8</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,14</t>
+          <t>-0,2; 3,81</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 2,53</t>
+          <t>-0,44; 2,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,22</t>
+          <t>-1,31; 1,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 2,82</t>
+          <t>0,13; 3,05</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-17,8%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>23,59%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>31,0%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>22,71%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>32,95%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-17,8%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 93,54</t>
+          <t>-20,73; 67,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,51; 75,67</t>
+          <t>-43,1; 26,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 104,43</t>
+          <t>-15,89; 77,43</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 62,89</t>
+          <t>-9,22; 98,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 17,25</t>
+          <t>-17,99; 80,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 74,45</t>
+          <t>-4,56; 110,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 61,28</t>
+          <t>-7,96; 58,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 29,33</t>
+          <t>-23,92; 30,0</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 65,02</t>
+          <t>2,11; 75,53</t>
         </is>
       </c>
     </row>
